--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1366,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118271145</v>
+        <v>66911818</v>
       </c>
       <c r="B8" t="n">
-        <v>97880</v>
+        <v>98271</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,26 +1401,25 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brattåkersberget, Vb</t>
+          <t>Brattåker, ängarna, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720949</v>
+        <v>720999</v>
       </c>
       <c r="R8" t="n">
-        <v>7136267</v>
+        <v>7136160</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,17 +1443,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2017-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2017-07-29</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>9 blommande, starkt doftande på kvällen</t>
+          <t>Årets slåtterinsats med Naturskyddsföreningen i Vindeln. Rapporterat av deltagande medlem Inger H.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,22 +1462,137 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Lage Sandgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lage Sandgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118271145</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97880</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Brattåkersberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>720949</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7136267</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>9 blommande, starkt doftande på kvällen</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Glenn Örnberg</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Glenn Örnberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -1369,7 +1369,7 @@
         <v>66911818</v>
       </c>
       <c r="B8" t="n">
-        <v>98271</v>
+        <v>98274</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -1369,7 +1369,7 @@
         <v>66911818</v>
       </c>
       <c r="B8" t="n">
-        <v>98274</v>
+        <v>98275</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -1369,7 +1369,7 @@
         <v>66911818</v>
       </c>
       <c r="B8" t="n">
-        <v>98275</v>
+        <v>98278</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1594,6 +1594,112 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122743381</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98278</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gräningen NÖ, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>721081</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7136282</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -1369,7 +1369,7 @@
         <v>66911818</v>
       </c>
       <c r="B8" t="n">
-        <v>98278</v>
+        <v>98381</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>122743381</v>
       </c>
       <c r="B10" t="n">
-        <v>98278</v>
+        <v>98381</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -1599,7 +1599,7 @@
         <v>122743381</v>
       </c>
       <c r="B10" t="n">
-        <v>98381</v>
+        <v>98389</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -1369,7 +1369,7 @@
         <v>66911818</v>
       </c>
       <c r="B8" t="n">
-        <v>98381</v>
+        <v>98389</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -1369,7 +1369,7 @@
         <v>66911818</v>
       </c>
       <c r="B8" t="n">
-        <v>98389</v>
+        <v>98391</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>122743381</v>
       </c>
       <c r="B10" t="n">
-        <v>98389</v>
+        <v>98391</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -1369,7 +1369,7 @@
         <v>66911818</v>
       </c>
       <c r="B8" t="n">
-        <v>98391</v>
+        <v>98399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>122743381</v>
       </c>
       <c r="B10" t="n">
-        <v>98391</v>
+        <v>98399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -1599,7 +1599,7 @@
         <v>122743381</v>
       </c>
       <c r="B10" t="n">
-        <v>98399</v>
+        <v>98402</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -1599,7 +1599,7 @@
         <v>122743381</v>
       </c>
       <c r="B10" t="n">
-        <v>98402</v>
+        <v>98404</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1700,6 +1700,117 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126499948</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98281</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Brattåker 2, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>721044</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7136130</v>
+      </c>
+      <c r="S11" t="n">
+        <v>100</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Längs stigen till Brattåker stugan och överallt på ängarna</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linus Karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linus Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1811,6 +1811,322 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126535233</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98395</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Brattåkersberget, Brattåkersberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>720923</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7136260</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Glenn Örnberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Glenn Örnberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126533977</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98395</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Brattåkersberget, Brattåkersberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>720955</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7136264</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Luktar ljuvligt</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Glenn Örnberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Glenn Örnberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126534938</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98395</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Brattåkersberget, Brattåkersberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>721021</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7136294</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Släkten komma och släkten gå</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Glenn Örnberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Glenn Örnberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -1816,7 +1816,7 @@
         <v>126535233</v>
       </c>
       <c r="B12" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>126533977</v>
       </c>
       <c r="B13" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>126534938</v>
       </c>
       <c r="B14" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -1816,7 +1816,7 @@
         <v>126535233</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>126533977</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>126534938</v>
       </c>
       <c r="B14" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -1816,7 +1816,7 @@
         <v>126535233</v>
       </c>
       <c r="B12" t="n">
-        <v>98476</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>126533977</v>
       </c>
       <c r="B13" t="n">
-        <v>98476</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>126534938</v>
       </c>
       <c r="B14" t="n">
-        <v>98476</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>229739</v>
       </c>
       <c r="B2" t="n">
-        <v>95596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720928.1306180274</v>
+        <v>720928</v>
       </c>
       <c r="R2" t="n">
-        <v>7136236.871519803</v>
+        <v>7136237</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -745,7 +740,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>AC-Vin-0006</t>
+          <t>Arkiv-AC-Vin-0021</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -753,19 +748,9 @@
           <t>1990-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1990-01-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,59 +780,63 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6871444</v>
+        <v>61022074</v>
       </c>
       <c r="B3" t="n">
-        <v>96252</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223591</v>
+        <v>100399</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Turkos blåvinge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Aricia nicias</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Meigen, 1829)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brattåkersberget, Vb</t>
+          <t>Brattåkern, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721016.1372165789</v>
+        <v>721274</v>
       </c>
       <c r="R3" t="n">
-        <v>7136159.964606497</v>
+        <v>7136169</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-07-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-07-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,65 +880,64 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sören Uppsäll, Per Nihlén, Henrik Sporrong</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6871471</v>
+        <v>61022075</v>
       </c>
       <c r="B4" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>102366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ängsmetallvinge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Adscita statices</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brattåkersberget, Vb</t>
+          <t>Brattåkern, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720979.446428127</v>
+        <v>720978</v>
       </c>
       <c r="R4" t="n">
-        <v>7136245.357668993</v>
+        <v>7136170</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,22 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-07-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-07-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,27 +981,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sören Uppsäll, Per Nihlén, Henrik Sporrong</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6871472</v>
+        <v>6871471</v>
       </c>
       <c r="B5" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721016.1372165789</v>
+        <v>720979</v>
       </c>
       <c r="R5" t="n">
-        <v>7136159.964606497</v>
+        <v>7136245</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,19 +1061,9 @@
           <t>2013-07-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-07-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,15 +1090,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6871446</v>
+        <v>6871472</v>
       </c>
       <c r="B6" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,19 +1101,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223597</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1173,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721025.7016511835</v>
+        <v>721016</v>
       </c>
       <c r="R6" t="n">
-        <v>7136130.145700037</v>
+        <v>7136160</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,19 +1158,9 @@
           <t>2013-07-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2013-07-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,62 +1187,56 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>61022074</v>
+        <v>118271145</v>
       </c>
       <c r="B7" t="n">
-        <v>42566</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100399</v>
+        <v>219874</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Turkos blåvinge</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Aricia nicias</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Meigen, 1829)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brattåkern, Vb</t>
+          <t>Brattåkersberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721273.8232865662</v>
+        <v>720949</v>
       </c>
       <c r="R7" t="n">
-        <v>7136168.933282379</v>
+        <v>7136267</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,22 +1260,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2016-07-10</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2016-07-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>9 blommande, starkt doftande på kvällen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,33 +1279,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Glenn Örnberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén, Henrik Sporrong</t>
+          <t>Glenn Örnberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66911818</v>
+        <v>122743381</v>
       </c>
       <c r="B8" t="n">
-        <v>98399</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,27 +1326,20 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brattåker, ängarna, Vb</t>
+          <t>Gräningen NÖ, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720999</v>
+        <v>721081</v>
       </c>
       <c r="R8" t="n">
-        <v>7136160</v>
+        <v>7136282</v>
       </c>
       <c r="S8" t="n">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1443,17 +1363,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-07-29</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-07-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Årets slåtterinsats med Naturskyddsföreningen i Vindeln. Rapporterat av deltagande medlem Inger H.</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,27 +1383,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lage Sandgren</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lage Sandgren</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118271145</v>
+        <v>126533977</v>
       </c>
       <c r="B9" t="n">
-        <v>97880</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,25 +1427,21 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brattåkersberget, Vb</t>
+          <t>Brattåkersberget, Brattåkersberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720949</v>
+        <v>720955</v>
       </c>
       <c r="R9" t="n">
-        <v>7136267</v>
+        <v>7136264</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,17 +1468,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>9 blommande, starkt doftande på kvällen</t>
+          <t>Luktar ljuvligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,15 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743381</v>
+        <v>126534938</v>
       </c>
       <c r="B10" t="n">
-        <v>98404</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,16 +1535,20 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gräningen NÖ, Vb</t>
+          <t>Brattåkersberget, Brattåkersberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721081</v>
+        <v>721021</v>
       </c>
       <c r="R10" t="n">
-        <v>7136282</v>
+        <v>7136294</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,12 +1575,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Släkten komma och släkten gå</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,32 +1594,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Glenn Örnberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Glenn Örnberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126499948</v>
+        <v>126535233</v>
       </c>
       <c r="B11" t="n">
-        <v>98281</v>
+        <v>99153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,45 +1624,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223597</v>
+        <v>219874</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Brattåker 2, Vb</t>
+          <t>Brattåkersberget, Brattåkersberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721044</v>
+        <v>720923</v>
       </c>
       <c r="R11" t="n">
-        <v>7136130</v>
+        <v>7136260</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1775,17 +1682,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Längs stigen till Brattåker stugan och överallt på ängarna</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,64 +1703,72 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linus Karlsson</t>
+          <t>Glenn Örnberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linus Karlsson</t>
+          <t>Glenn Örnberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126535233</v>
+        <v>125245631</v>
       </c>
       <c r="B12" t="n">
-        <v>98476</v>
+        <v>98050</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>222112</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brattåkersberget, Brattåkersberget, Vb</t>
+          <t>Brattåker, 75 m söder om stugan, Hällnäs, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720923</v>
+        <v>720968</v>
       </c>
       <c r="R12" t="n">
-        <v>7136260</v>
+        <v>7136109</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1882,12 +1792,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,64 +1813,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Glenn Örnberg</t>
+          <t>Henrik Sporrong</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Glenn Örnberg</t>
+          <t>Henrik Sporrong</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126533977</v>
+        <v>134037209</v>
       </c>
       <c r="B13" t="n">
-        <v>98476</v>
+        <v>98127</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>222112</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Brattåkersberget, Brattåkersberget, Vb</t>
+          <t>Brattåker, 75 m söder om stugan, Brattåker, 75 m söder om stugan, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720955</v>
+        <v>720971</v>
       </c>
       <c r="R13" t="n">
-        <v>7136264</v>
+        <v>7136139</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1984,17 +1890,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Luktar ljuvligt</t>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,29 +1914,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Glenn Örnberg</t>
+          <t>Henrik Sporrong</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Glenn Örnberg</t>
+          <t>Henrik Sporrong</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126534938</v>
+        <v>6871444</v>
       </c>
       <c r="B14" t="n">
-        <v>98476</v>
+        <v>99036</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,38 +1943,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219874</v>
+        <v>223591</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Brattåkersberget, Brattåkersberget, Vb</t>
+          <t>Brattåkersberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721021</v>
+        <v>721016</v>
       </c>
       <c r="R14" t="n">
-        <v>7136294</v>
+        <v>7136160</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2091,17 +1997,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2013-07-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Släkten komma och släkten gå</t>
+          <t>2013-07-02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,22 +2011,114 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Glenn Örnberg</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Glenn Örnberg</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6871446</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Brattåkersberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>721026</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7136130</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2013-07-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2013-07-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50665-2023 artfynd.xlsx
+++ b/artfynd/A 50665-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/229739</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61022074</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61022075</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6871471</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6871472</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118271145</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743381</t>
         </is>
       </c>
     </row>
@@ -1503,6 +1543,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533977</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126534938</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126535233</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1822,6 +1877,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125245631</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1929,6 +1989,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134037209</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2026,6 +2091,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6871444</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2119,8 +2189,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6871446</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>